--- a/Master Document List.xlsx
+++ b/Master Document List.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t xml:space="preserve">MDL Code</t>
   </si>
@@ -55,6 +55,21 @@
     <t xml:space="preserve">Design lead</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Permanent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA-0002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA-0002-Test Plan Log Template.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design Lead</t>
+  </si>
+  <si>
     <t xml:space="preserve">SOPs</t>
   </si>
   <si>
@@ -70,10 +85,13 @@
     <t xml:space="preserve">P1012202501-1 Revision 2 Test Plan.docx</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1012202501-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1012202501-2 Revision 2 Test Log.xlsx</t>
   </si>
 </sst>
 </file>
@@ -88,6 +106,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -160,20 +179,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -363,438 +386,468 @@
   <dimension ref="A7:M66"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.09"/>
   </cols>
   <sheetData>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2" t="s">
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="A10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2" t="s">
+      <c r="M62" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2" t="n">
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L62" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
+      <c r="L63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3"/>
+      <c r="L65" s="3"/>
+      <c r="M65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="48">
